--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -414,9 +414,6 @@
     <t>frDicomSOPInstanceObservation</t>
   </si>
   <si>
-    <t>Conformité FR-DICOM-SOP-instrance-observation (CI-SIS) </t>
-  </si>
-  <si>
     <t>Conformité FR-DICOM-SOP-instrance-observation (CI-SIS)</t>
   </si>
   <si>
@@ -460,9 +457,6 @@
   </si>
   <si>
     <t>dicomSOPInstanceObservation</t>
-  </si>
-  <si>
-    <t>Conformité SOP Instance Observation (DICOM Part 20) </t>
   </si>
   <si>
     <t>Conformité SOP Instance Observation (DICOM Part 20)</t>
@@ -671,7 +665,7 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve"> url permettant d’accéder aux images sur la Drim box source. Cette url, basée sur le profil IHE Invoke Image Display , est construite de la manière suivante :https://&lt;location&gt;/IHEInvokeImageDisplay?requestType=STUDY&amp;amp;studyUID=&lt;StudyInstanceUID&gt;&amp;amp;Accessionnumber=&lt;Accessionnumber&gt;&amp;amp;idCDA=&lt;idCDA&gt; avec les paramètres :&lt;location&gt; : Racine de l’URL par laquelle on accède au PACS qui met à disposition de l’examen (cf volet CI-SIS_SPEC_TECH_Objet ref d'examens d'imagerie)&lt;StudyInstanceUID&gt; : Identifiant de l’examen attribué par le RIS&lt;Accessionnumber&gt; : Identifiant de la demande attribué par le RIS (concaténer root.extension)&lt;idCDA&gt; : Identifiant du document CDA IMG-CR-IMG (élément &lt;id root&gt;)</t>
+    <t>url permettant d’accéder aux images sur la Drim box source. Cette url, basée sur le profil IHE Invoke Image Display , est construite de la manière suivante :https://&lt;location&gt;/IHEInvokeImageDisplay?requestType=STUDY&amp;amp;studyUID=&lt;StudyInstanceUID&gt;&amp;amp;Accessionnumber=&lt;Accessionnumber&gt;&amp;amp;idCDA=&lt;idCDA&gt; avec les paramètres :&lt;location&gt; : Racine de l’URL par laquelle on accède au PACS qui met à disposition de l’examen (cf volet CI-SIS_SPEC_TECH_Objet ref d'examens d'imagerie)&lt;StudyInstanceUID&gt; : Identifiant de l’examen attribué par le RIS&lt;Accessionnumber&gt; : Identifiant de la demande attribué par le RIS (concaténer root.extension)&lt;idCDA&gt; : Identifiant du document CDA IMG-CR-IMG (élément &lt;id root&gt;)</t>
   </si>
   <si>
     <t>Url permettant d’accéder aux images sur la Drim box source</t>
@@ -851,7 +845,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -2959,7 +2953,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3030,10 +3024,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3131,10 +3125,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3234,10 +3228,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3337,10 +3331,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3369,7 +3363,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3381,7 +3375,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3440,10 +3434,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3543,13 +3537,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3574,10 +3568,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3648,10 +3642,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3749,10 +3743,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3852,10 +3846,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3955,10 +3949,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3987,7 +3981,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3999,7 +3993,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -4058,10 +4052,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4161,10 +4155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4178,7 +4172,7 @@
         <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -4201,7 +4195,7 @@
         <v>75</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>75</v>
@@ -4220,7 +4214,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -4238,7 +4232,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4258,10 +4252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4275,7 +4269,7 @@
         <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>75</v>
@@ -4298,7 +4292,7 @@
         <v>75</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>75</v>
@@ -4317,7 +4311,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4335,7 +4329,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4355,10 +4349,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4434,7 +4428,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4454,10 +4448,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4471,7 +4465,7 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4483,10 +4477,10 @@
         <v>96</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4537,7 +4531,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4557,10 +4551,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4583,7 +4577,7 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -4636,7 +4630,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4656,10 +4650,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4673,7 +4667,7 @@
         <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>75</v>
@@ -4682,13 +4676,13 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4719,7 +4713,7 @@
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4737,7 +4731,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4757,10 +4751,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4858,10 +4852,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4877,7 +4871,7 @@
         <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -4890,7 +4884,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4941,7 +4935,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4961,17 +4955,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>76</v>
@@ -4980,7 +4974,7 @@
         <v>76</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -4993,7 +4987,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5044,7 +5038,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5064,17 +5058,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>81</v>
@@ -5096,7 +5090,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5147,7 +5141,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5167,17 +5161,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>81</v>
@@ -5199,7 +5193,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5250,7 +5244,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5270,17 +5264,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>81</v>
@@ -5289,7 +5283,7 @@
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -5302,7 +5296,7 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5353,7 +5347,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5373,10 +5367,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5399,11 +5393,11 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5454,7 +5448,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5474,10 +5468,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5504,7 +5498,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5555,7 +5549,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5575,17 +5569,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5603,11 +5597,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5658,7 +5652,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5678,17 +5672,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5706,11 +5700,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5761,7 +5755,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5781,17 +5775,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5809,11 +5803,11 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5864,7 +5858,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5884,10 +5878,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5910,7 +5904,7 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5963,7 +5957,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5983,10 +5977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6000,7 +5994,7 @@
         <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>75</v>
@@ -6009,13 +6003,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6066,7 +6060,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6086,10 +6080,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6187,17 +6181,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -6219,7 +6213,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6250,7 +6244,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6268,7 +6262,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6288,17 +6282,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6316,11 +6310,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6371,7 +6365,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6391,17 +6385,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>81</v>
@@ -6423,7 +6417,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6454,7 +6448,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6472,7 +6466,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6492,17 +6486,17 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>81</v>
@@ -6524,7 +6518,7 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6575,7 +6569,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6595,17 +6589,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>81</v>
@@ -6627,7 +6621,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6639,7 +6633,7 @@
         <v>75</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>75</v>
@@ -6654,11 +6648,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6676,7 +6670,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6696,10 +6690,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6755,7 +6749,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -6773,7 +6767,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6793,10 +6787,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6822,13 +6816,13 @@
         <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6878,7 +6872,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6898,41 +6892,41 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="F51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="M51" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6983,7 +6977,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7003,17 +6997,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -7031,11 +7025,11 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7086,7 +7080,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7098,7 +7092,7 @@
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
@@ -7106,10 +7100,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7165,7 +7159,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7183,7 +7177,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7203,10 +7197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7220,7 +7214,7 @@
         <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>75</v>
@@ -7229,13 +7223,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7286,7 +7280,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7306,10 +7300,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7332,7 +7326,7 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7361,11 +7355,11 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7383,7 +7377,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7403,10 +7397,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7429,7 +7423,7 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7482,7 +7476,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7502,10 +7496,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7561,7 +7555,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7579,7 +7573,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7599,10 +7593,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7625,7 +7619,7 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7678,7 +7672,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7698,10 +7692,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7724,7 +7718,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7757,7 +7751,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -7775,7 +7769,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7795,10 +7789,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7821,7 +7815,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7850,11 +7844,11 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7872,7 +7866,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7892,10 +7886,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7918,11 +7912,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7973,7 +7967,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7993,10 +7987,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8019,7 +8013,7 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -8072,7 +8066,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8092,10 +8086,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8118,7 +8112,7 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8171,7 +8165,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8191,10 +8185,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8217,7 +8211,7 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8270,7 +8264,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8290,10 +8284,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8316,7 +8310,7 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8369,7 +8363,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8389,10 +8383,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8415,7 +8409,7 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8468,7 +8462,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8488,10 +8482,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8514,7 +8508,7 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8567,7 +8561,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8587,10 +8581,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8604,7 +8598,7 @@
         <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -8613,7 +8607,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8654,7 +8648,7 @@
         <v>75</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
@@ -8664,7 +8658,7 @@
         <v>125</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8684,13 +8678,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>75</v>
@@ -8712,10 +8706,10 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -8767,7 +8761,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8787,10 +8781,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8888,10 +8882,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8989,10 +8983,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9090,10 +9084,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9191,10 +9185,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9294,10 +9288,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9397,10 +9391,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9500,10 +9494,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9603,10 +9597,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9704,10 +9698,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9744,7 +9738,7 @@
         <v>75</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>75</v>
@@ -9763,7 +9757,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9781,7 +9775,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -9801,10 +9795,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9831,7 +9825,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9882,7 +9876,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9902,10 +9896,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9932,12 +9926,12 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -9983,7 +9977,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -10003,10 +9997,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10082,7 +10076,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -10102,10 +10096,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10128,7 +10122,7 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10181,7 +10175,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10201,10 +10195,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10227,7 +10221,7 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10280,7 +10274,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10300,10 +10294,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10326,7 +10320,7 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10379,7 +10373,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10399,10 +10393,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10425,7 +10419,7 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10478,7 +10472,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10498,10 +10492,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10524,7 +10518,7 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10577,7 +10571,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10597,10 +10591,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10623,7 +10617,7 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10676,7 +10670,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10696,10 +10690,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10722,7 +10716,7 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10775,7 +10769,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -10795,10 +10789,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10821,7 +10815,7 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10874,7 +10868,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10894,10 +10888,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10920,7 +10914,7 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10973,7 +10967,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10993,10 +10987,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11019,7 +11013,7 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11072,7 +11066,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11092,10 +11086,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11118,7 +11112,7 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11171,7 +11165,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11191,13 +11185,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>75</v>
@@ -11219,10 +11213,10 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -11274,7 +11268,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11294,10 +11288,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11395,10 +11389,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11496,10 +11490,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11597,10 +11591,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11698,10 +11692,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11801,10 +11795,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11904,10 +11898,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12007,10 +12001,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12110,10 +12104,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12211,10 +12205,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12270,7 +12264,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>75</v>
@@ -12288,7 +12282,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -12308,10 +12302,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12338,7 +12332,7 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12389,7 +12383,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12409,10 +12403,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12439,12 +12433,12 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12490,7 +12484,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12510,10 +12504,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12589,7 +12583,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -12609,10 +12603,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12635,7 +12629,7 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12688,7 +12682,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12708,10 +12702,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12734,7 +12728,7 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12787,7 +12781,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -12807,10 +12801,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12833,7 +12827,7 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12886,7 +12880,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -12906,10 +12900,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12932,7 +12926,7 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12985,7 +12979,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13005,10 +12999,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13031,7 +13025,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13084,7 +13078,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13104,10 +13098,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13130,7 +13124,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13183,7 +13177,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13203,10 +13197,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13229,7 +13223,7 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13282,7 +13276,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13302,10 +13296,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13328,7 +13322,7 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13381,7 +13375,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13401,10 +13395,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13427,7 +13421,7 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13480,7 +13474,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -13500,10 +13494,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13526,7 +13520,7 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13579,7 +13573,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13599,10 +13593,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13625,7 +13619,7 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13678,7 +13672,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -13698,13 +13692,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>75</v>
@@ -13726,10 +13720,10 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -13781,7 +13775,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -13801,10 +13795,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13902,10 +13896,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14003,10 +13997,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14104,10 +14098,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14205,10 +14199,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14308,10 +14302,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14411,10 +14405,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14514,10 +14508,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14617,10 +14611,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14718,10 +14712,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14758,7 +14752,7 @@
         <v>75</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>75</v>
@@ -14777,7 +14771,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>75</v>
@@ -14795,7 +14789,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -14815,10 +14809,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14845,7 +14839,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14896,7 +14890,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -14916,10 +14910,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14946,12 +14940,12 @@
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
@@ -14997,7 +14991,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15017,10 +15011,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15096,7 +15090,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15116,10 +15110,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15142,7 +15136,7 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15195,7 +15189,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15215,10 +15209,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15241,7 +15235,7 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15294,7 +15288,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -15314,10 +15308,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15340,7 +15334,7 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15393,7 +15387,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -15413,10 +15407,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15439,7 +15433,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15492,7 +15486,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -15512,10 +15506,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15538,7 +15532,7 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15591,7 +15585,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -15611,10 +15605,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15637,7 +15631,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15690,7 +15684,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -15710,10 +15704,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15736,7 +15730,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15789,7 +15783,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -15809,10 +15803,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15835,7 +15829,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15888,7 +15882,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -15908,10 +15902,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15934,7 +15928,7 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -15987,7 +15981,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16007,10 +16001,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16033,7 +16027,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16086,7 +16080,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16106,10 +16100,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16132,7 +16126,7 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16185,7 +16179,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16205,10 +16199,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16231,7 +16225,7 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16284,7 +16278,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16304,10 +16298,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16330,7 +16324,7 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16383,7 +16377,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16403,10 +16397,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16429,7 +16423,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16482,7 +16476,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -16502,10 +16496,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16528,11 +16522,11 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -16583,7 +16577,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -16603,10 +16597,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16704,10 +16698,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16805,10 +16799,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16906,10 +16900,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17007,10 +17001,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17110,10 +17104,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17213,10 +17207,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17316,10 +17310,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17419,10 +17413,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17520,10 +17514,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17557,7 +17551,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>75</v>
@@ -17579,7 +17573,7 @@
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>75</v>
@@ -17597,7 +17591,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -17617,10 +17611,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17643,7 +17637,7 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17696,7 +17690,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -17716,10 +17710,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17742,7 +17736,7 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17795,7 +17789,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
